--- a/artfynd/A 52918-2024 artfynd.xlsx
+++ b/artfynd/A 52918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121561843</v>
+        <v>121561863</v>
       </c>
       <c r="B2" t="n">
-        <v>98104</v>
+        <v>90739</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586348</v>
+        <v>586366</v>
       </c>
       <c r="R2" t="n">
-        <v>6382819</v>
+        <v>6382808</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121561822</v>
+        <v>121561809</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>92030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,46 +801,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>a 52918, Boarum, Sm</t>
+          <t>A A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586360</v>
+        <v>586380</v>
       </c>
       <c r="R3" t="n">
-        <v>6382810</v>
+        <v>6382811</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,6 +876,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mkt anfrätt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121561809</v>
+        <v>121561912</v>
       </c>
       <c r="B4" t="n">
-        <v>92030</v>
+        <v>91115</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,21 +948,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A A 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586380</v>
+        <v>586418</v>
       </c>
       <c r="R4" t="n">
-        <v>6382811</v>
+        <v>6382735</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +999,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mkt anfrätt</t>
+          <t>Död gren på levande tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1130,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121561790</v>
+        <v>121561822</v>
       </c>
       <c r="B6" t="n">
-        <v>90739</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,49 +1153,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>a 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586486</v>
+        <v>586360</v>
       </c>
       <c r="R6" t="n">
-        <v>6382734</v>
+        <v>6382810</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121561833</v>
+        <v>121561977</v>
       </c>
       <c r="B7" t="n">
-        <v>98104</v>
+        <v>57724</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,35 +1264,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1292,13 +1300,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586357</v>
+        <v>586491</v>
       </c>
       <c r="R7" t="n">
-        <v>6382811</v>
+        <v>6382667</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,7 +1344,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1355,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121561977</v>
+        <v>121561790</v>
       </c>
       <c r="B8" t="n">
-        <v>57724</v>
+        <v>90739</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,35 +1374,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1403,13 +1413,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586491</v>
+        <v>586486</v>
       </c>
       <c r="R8" t="n">
-        <v>6382667</v>
+        <v>6382734</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,6 +1457,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1465,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121561912</v>
+        <v>121561843</v>
       </c>
       <c r="B9" t="n">
-        <v>91115</v>
+        <v>98104</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,38 +1488,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1516,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586418</v>
+        <v>586348</v>
       </c>
       <c r="R9" t="n">
-        <v>6382735</v>
+        <v>6382819</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,11 +1560,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Död gren på levande tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121561956</v>
+        <v>121561833</v>
       </c>
       <c r="B10" t="n">
-        <v>57361</v>
+        <v>98104</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,39 +1599,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1636,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586567</v>
+        <v>586357</v>
       </c>
       <c r="R10" t="n">
-        <v>6382636</v>
+        <v>6382811</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,17 +1673,13 @@
           <t>2024-12-11</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>I murken björkstubbe. Kanske använt 2024?</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1703,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121561863</v>
+        <v>121561956</v>
       </c>
       <c r="B11" t="n">
-        <v>90739</v>
+        <v>57361</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,34 +1714,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1754,10 +1750,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586366</v>
+        <v>586567</v>
       </c>
       <c r="R11" t="n">
-        <v>6382808</v>
+        <v>6382636</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,13 +1788,17 @@
           <t>2024-12-11</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>I murken björkstubbe. Kanske använt 2024?</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52918-2024 artfynd.xlsx
+++ b/artfynd/A 52918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121561863</v>
+        <v>121561977</v>
       </c>
       <c r="B2" t="n">
-        <v>90739</v>
+        <v>57725</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586366</v>
+        <v>586491</v>
       </c>
       <c r="R2" t="n">
-        <v>6382808</v>
+        <v>6382667</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121561809</v>
+        <v>121561912</v>
       </c>
       <c r="B3" t="n">
-        <v>92030</v>
+        <v>91116</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,21 +825,21 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A A 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586380</v>
+        <v>586418</v>
       </c>
       <c r="R3" t="n">
-        <v>6382811</v>
+        <v>6382735</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Mkt anfrätt</t>
+          <t>Död gren på levande tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121561912</v>
+        <v>121561790</v>
       </c>
       <c r="B4" t="n">
-        <v>91115</v>
+        <v>90740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -948,7 +944,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -959,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586418</v>
+        <v>586486</v>
       </c>
       <c r="R4" t="n">
-        <v>6382735</v>
+        <v>6382734</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,11 +991,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Död gren på levande tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +1021,7 @@
         <v>121561974</v>
       </c>
       <c r="B5" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1144,7 +1135,7 @@
         <v>121561822</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1252,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121561977</v>
+        <v>121561863</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>90740</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,35 +1255,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1300,13 +1294,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586491</v>
+        <v>586366</v>
       </c>
       <c r="R7" t="n">
-        <v>6382667</v>
+        <v>6382808</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,6 +1338,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1362,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121561790</v>
+        <v>121561809</v>
       </c>
       <c r="B8" t="n">
-        <v>90739</v>
+        <v>92031</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1409,14 +1404,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>A A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586486</v>
+        <v>586380</v>
       </c>
       <c r="R8" t="n">
-        <v>6382734</v>
+        <v>6382811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,6 +1444,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mkt anfrätt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121561843</v>
+        <v>121561833</v>
       </c>
       <c r="B9" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586348</v>
+        <v>586357</v>
       </c>
       <c r="R9" t="n">
-        <v>6382819</v>
+        <v>6382811</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121561833</v>
+        <v>121561843</v>
       </c>
       <c r="B10" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586357</v>
+        <v>586348</v>
       </c>
       <c r="R10" t="n">
-        <v>6382811</v>
+        <v>6382819</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1701,7 +1701,7 @@
         <v>121561956</v>
       </c>
       <c r="B11" t="n">
-        <v>57361</v>
+        <v>57362</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 52918-2024 artfynd.xlsx
+++ b/artfynd/A 52918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121561977</v>
+        <v>121561822</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>a 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586491</v>
+        <v>586360</v>
       </c>
       <c r="R2" t="n">
-        <v>6382667</v>
+        <v>6382810</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121561912</v>
+        <v>121561809</v>
       </c>
       <c r="B3" t="n">
-        <v>91116</v>
+        <v>92031</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4217</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,21 +826,21 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>A A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586418</v>
+        <v>586380</v>
       </c>
       <c r="R3" t="n">
-        <v>6382735</v>
+        <v>6382811</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +877,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Död gren på levande tall</t>
+          <t>Mkt anfrätt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121561790</v>
+        <v>121561974</v>
       </c>
       <c r="B4" t="n">
-        <v>90740</v>
+        <v>57509</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +921,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586486</v>
+        <v>586491</v>
       </c>
       <c r="R4" t="n">
-        <v>6382734</v>
+        <v>6382667</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +1001,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121561974</v>
+        <v>121561977</v>
       </c>
       <c r="B5" t="n">
-        <v>57509</v>
+        <v>57725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,37 +1031,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1132,7 +1129,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121561822</v>
+        <v>121561833</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1176,14 +1173,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>a 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586360</v>
+        <v>586357</v>
       </c>
       <c r="R6" t="n">
-        <v>6382810</v>
+        <v>6382811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1240,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121561863</v>
+        <v>121561790</v>
       </c>
       <c r="B7" t="n">
         <v>90740</v>
@@ -1278,7 +1275,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1294,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586366</v>
+        <v>586486</v>
       </c>
       <c r="R7" t="n">
-        <v>6382808</v>
+        <v>6382734</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121561809</v>
+        <v>121561956</v>
       </c>
       <c r="B8" t="n">
-        <v>92031</v>
+        <v>57362</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1370,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1395,23 +1392,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A A 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586380</v>
+        <v>586567</v>
       </c>
       <c r="R8" t="n">
-        <v>6382811</v>
+        <v>6382636</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,7 +1446,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Mkt anfrätt</t>
+          <t>I murken björkstubbe. Kanske använt 2024?</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,7 +1455,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1476,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121561833</v>
+        <v>121561863</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>90740</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,35 +1485,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586357</v>
+        <v>586366</v>
       </c>
       <c r="R9" t="n">
-        <v>6382811</v>
+        <v>6382808</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121561843</v>
+        <v>121561912</v>
       </c>
       <c r="B10" t="n">
-        <v>98105</v>
+        <v>91116</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,35 +1599,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1635,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586348</v>
+        <v>586418</v>
       </c>
       <c r="R10" t="n">
-        <v>6382819</v>
+        <v>6382735</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,6 +1674,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Död gren på levande tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121561956</v>
+        <v>121561843</v>
       </c>
       <c r="B11" t="n">
-        <v>57362</v>
+        <v>98105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,39 +1718,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1750,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586567</v>
+        <v>586348</v>
       </c>
       <c r="R11" t="n">
-        <v>6382636</v>
+        <v>6382819</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,17 +1792,13 @@
           <t>2024-12-11</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>I murken björkstubbe. Kanske använt 2024?</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52918-2024 artfynd.xlsx
+++ b/artfynd/A 52918-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121561822</v>
+        <v>121561843</v>
       </c>
       <c r="B2" t="n">
         <v>98105</v>
@@ -719,14 +719,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>a 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586360</v>
+        <v>586348</v>
       </c>
       <c r="R2" t="n">
-        <v>6382810</v>
+        <v>6382819</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121561809</v>
+        <v>121561833</v>
       </c>
       <c r="B3" t="n">
-        <v>92031</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,46 +798,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A A 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586380</v>
+        <v>586357</v>
       </c>
       <c r="R3" t="n">
         <v>6382811</v>
@@ -873,11 +870,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Mkt anfrätt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121561974</v>
+        <v>121561977</v>
       </c>
       <c r="B4" t="n">
-        <v>57509</v>
+        <v>57725</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,37 +909,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1019,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121561977</v>
+        <v>121561809</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>92031</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,49 +1019,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>A A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586491</v>
+        <v>586380</v>
       </c>
       <c r="R5" t="n">
-        <v>6382667</v>
+        <v>6382811</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,12 +1096,18 @@
           <t>2024-12-11</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mkt anfrätt</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121561833</v>
+        <v>121561822</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1173,14 +1170,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>a 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586357</v>
+        <v>586360</v>
       </c>
       <c r="R6" t="n">
-        <v>6382811</v>
+        <v>6382810</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1237,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121561790</v>
+        <v>121561863</v>
       </c>
       <c r="B7" t="n">
         <v>90740</v>
@@ -1275,7 +1272,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1291,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586486</v>
+        <v>586366</v>
       </c>
       <c r="R7" t="n">
-        <v>6382734</v>
+        <v>6382808</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121561956</v>
+        <v>121561790</v>
       </c>
       <c r="B8" t="n">
-        <v>57362</v>
+        <v>90740</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1392,13 +1389,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1406,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586567</v>
+        <v>586486</v>
       </c>
       <c r="R8" t="n">
-        <v>6382636</v>
+        <v>6382734</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,17 +1440,13 @@
           <t>2024-12-11</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>I murken björkstubbe. Kanske använt 2024?</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1473,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121561863</v>
+        <v>121561912</v>
       </c>
       <c r="B9" t="n">
-        <v>90740</v>
+        <v>91116</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,35 +1477,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>4217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1524,10 +1516,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586366</v>
+        <v>586418</v>
       </c>
       <c r="R9" t="n">
-        <v>6382808</v>
+        <v>6382735</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,6 +1552,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Död gren på levande tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121561912</v>
+        <v>121561956</v>
       </c>
       <c r="B10" t="n">
-        <v>91116</v>
+        <v>57362</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,25 +1596,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4217</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1625,12 +1622,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1638,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586418</v>
+        <v>586567</v>
       </c>
       <c r="R10" t="n">
-        <v>6382735</v>
+        <v>6382636</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1676,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Död gren på levande tall</t>
+          <t>I murken björkstubbe. Kanske använt 2024?</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,7 +1685,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1706,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121561843</v>
+        <v>121561974</v>
       </c>
       <c r="B11" t="n">
-        <v>98105</v>
+        <v>57509</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,35 +1715,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1754,13 +1755,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586348</v>
+        <v>586491</v>
       </c>
       <c r="R11" t="n">
-        <v>6382819</v>
+        <v>6382667</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1798,7 +1799,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52918-2024 artfynd.xlsx
+++ b/artfynd/A 52918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121561843</v>
+        <v>121561912</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>91116</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586348</v>
+        <v>586418</v>
       </c>
       <c r="R2" t="n">
-        <v>6382819</v>
+        <v>6382735</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +762,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Död gren på levande tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -897,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121561977</v>
+        <v>121561956</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57362</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,20 +917,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -930,12 +938,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -945,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586491</v>
+        <v>586567</v>
       </c>
       <c r="R4" t="n">
-        <v>6382667</v>
+        <v>6382636</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,6 +993,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I murken björkstubbe. Kanske använt 2024?</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121561809</v>
+        <v>121561974</v>
       </c>
       <c r="B5" t="n">
-        <v>92031</v>
+        <v>57509</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,48 +1040,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A A 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586380</v>
+        <v>586491</v>
       </c>
       <c r="R5" t="n">
-        <v>6382811</v>
+        <v>6382667</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,18 +1114,12 @@
           <t>2024-12-11</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mkt anfrätt</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1126,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121561822</v>
+        <v>121561863</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>90740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,46 +1150,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>a 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586360</v>
+        <v>586366</v>
       </c>
       <c r="R6" t="n">
-        <v>6382810</v>
+        <v>6382808</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1252,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121561863</v>
+        <v>121561790</v>
       </c>
       <c r="B7" t="n">
         <v>90740</v>
@@ -1272,7 +1287,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1288,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586366</v>
+        <v>586486</v>
       </c>
       <c r="R7" t="n">
-        <v>6382808</v>
+        <v>6382734</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121561790</v>
+        <v>121561822</v>
       </c>
       <c r="B8" t="n">
-        <v>90740</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,49 +1378,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>a 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586486</v>
+        <v>586360</v>
       </c>
       <c r="R8" t="n">
-        <v>6382734</v>
+        <v>6382810</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121561912</v>
+        <v>121561843</v>
       </c>
       <c r="B9" t="n">
-        <v>91116</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,38 +1489,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1516,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586418</v>
+        <v>586348</v>
       </c>
       <c r="R9" t="n">
-        <v>6382735</v>
+        <v>6382819</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,11 +1561,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Död gren på levande tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121561956</v>
+        <v>121561809</v>
       </c>
       <c r="B10" t="n">
-        <v>57362</v>
+        <v>92031</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,21 +1604,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1622,24 +1626,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>A A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586567</v>
+        <v>586380</v>
       </c>
       <c r="R10" t="n">
-        <v>6382636</v>
+        <v>6382811</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1679,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I murken björkstubbe. Kanske använt 2024?</t>
+          <t>Mkt anfrätt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,6 +1688,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1703,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121561974</v>
+        <v>121561977</v>
       </c>
       <c r="B11" t="n">
-        <v>57509</v>
+        <v>57725</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,37 +1719,33 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>

--- a/artfynd/A 52918-2024 artfynd.xlsx
+++ b/artfynd/A 52918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121561912</v>
+        <v>121561833</v>
       </c>
       <c r="B2" t="n">
-        <v>91116</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586418</v>
+        <v>586357</v>
       </c>
       <c r="R2" t="n">
-        <v>6382735</v>
+        <v>6382811</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Död gren på levande tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121561833</v>
+        <v>121561956</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>57363</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,35 +798,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586357</v>
+        <v>586567</v>
       </c>
       <c r="R3" t="n">
-        <v>6382811</v>
+        <v>6382636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,13 +876,17 @@
           <t>2024-12-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I murken björkstubbe. Kanske använt 2024?</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121561956</v>
+        <v>121561912</v>
       </c>
       <c r="B4" t="n">
-        <v>57362</v>
+        <v>91124</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,25 +917,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,13 +943,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586567</v>
+        <v>586418</v>
       </c>
       <c r="R4" t="n">
-        <v>6382636</v>
+        <v>6382735</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +996,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I murken björkstubbe. Kanske använt 2024?</t>
+          <t>Död gren på levande tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,6 +1005,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121561974</v>
+        <v>121561977</v>
       </c>
       <c r="B5" t="n">
-        <v>57509</v>
+        <v>57726</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,37 +1036,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1141,7 +1137,7 @@
         <v>121561863</v>
       </c>
       <c r="B6" t="n">
-        <v>90740</v>
+        <v>90748</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1252,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121561790</v>
+        <v>121561809</v>
       </c>
       <c r="B7" t="n">
-        <v>90740</v>
+        <v>92039</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,21 +1264,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,14 +1295,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>A A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586486</v>
+        <v>586380</v>
       </c>
       <c r="R7" t="n">
-        <v>6382734</v>
+        <v>6382811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,6 +1335,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mkt anfrätt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121561822</v>
+        <v>121561790</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>90748</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,46 +1379,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>a 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586360</v>
+        <v>586486</v>
       </c>
       <c r="R8" t="n">
-        <v>6382810</v>
+        <v>6382734</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121561843</v>
+        <v>121561822</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,14 +1525,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>a 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586348</v>
+        <v>586360</v>
       </c>
       <c r="R9" t="n">
-        <v>6382819</v>
+        <v>6382810</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121561809</v>
+        <v>121561974</v>
       </c>
       <c r="B10" t="n">
-        <v>92031</v>
+        <v>57510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,48 +1608,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A A 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586380</v>
+        <v>586491</v>
       </c>
       <c r="R10" t="n">
-        <v>6382811</v>
+        <v>6382667</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,18 +1682,12 @@
           <t>2024-12-11</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mkt anfrätt</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1707,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121561977</v>
+        <v>121561843</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,35 +1718,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1755,13 +1754,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586491</v>
+        <v>586348</v>
       </c>
       <c r="R11" t="n">
-        <v>6382667</v>
+        <v>6382819</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,6 +1798,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52918-2024 artfynd.xlsx
+++ b/artfynd/A 52918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121561977</v>
+        <v>121561912</v>
       </c>
       <c r="B2" t="n">
-        <v>57726</v>
+        <v>91124</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586491</v>
+        <v>586418</v>
       </c>
       <c r="R2" t="n">
-        <v>6382667</v>
+        <v>6382735</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,12 +764,18 @@
           <t>2024-12-11</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Död gren på levande tall</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121561833</v>
+        <v>121561843</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -833,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586357</v>
+        <v>586348</v>
       </c>
       <c r="R3" t="n">
-        <v>6382811</v>
+        <v>6382819</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121561863</v>
+        <v>121561956</v>
       </c>
       <c r="B4" t="n">
-        <v>90748</v>
+        <v>57363</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,34 +921,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586366</v>
+        <v>586567</v>
       </c>
       <c r="R4" t="n">
-        <v>6382808</v>
+        <v>6382636</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,13 +995,17 @@
           <t>2024-12-11</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I murken björkstubbe. Kanske använt 2024?</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121561912</v>
+        <v>121561863</v>
       </c>
       <c r="B5" t="n">
-        <v>91124</v>
+        <v>90748</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,35 +1036,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1061,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586418</v>
+        <v>586366</v>
       </c>
       <c r="R5" t="n">
-        <v>6382735</v>
+        <v>6382808</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,11 +1111,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Död gren på levande tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121561956</v>
+        <v>121561809</v>
       </c>
       <c r="B6" t="n">
-        <v>57363</v>
+        <v>92039</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1167,24 +1176,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>A A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586567</v>
+        <v>586380</v>
       </c>
       <c r="R6" t="n">
-        <v>6382636</v>
+        <v>6382811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1229,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I murken björkstubbe. Kanske använt 2024?</t>
+          <t>Mkt anfrätt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,6 +1238,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1362,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121561974</v>
+        <v>121561977</v>
       </c>
       <c r="B8" t="n">
-        <v>57510</v>
+        <v>57726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,37 +1383,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1476,7 +1481,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121561822</v>
+        <v>121561833</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1520,14 +1525,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>a 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586360</v>
+        <v>586357</v>
       </c>
       <c r="R9" t="n">
-        <v>6382810</v>
+        <v>6382811</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121561843</v>
+        <v>121561974</v>
       </c>
       <c r="B10" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,35 +1604,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1635,13 +1644,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586348</v>
+        <v>586491</v>
       </c>
       <c r="R10" t="n">
-        <v>6382819</v>
+        <v>6382667</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1679,7 +1688,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1698,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121561809</v>
+        <v>121561822</v>
       </c>
       <c r="B11" t="n">
-        <v>92039</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,49 +1718,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A A 52918, Boarum, Sm</t>
+          <t>a 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586380</v>
+        <v>586360</v>
       </c>
       <c r="R11" t="n">
-        <v>6382811</v>
+        <v>6382810</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,11 +1790,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Mkt anfrätt</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 52918-2024 artfynd.xlsx
+++ b/artfynd/A 52918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121561912</v>
+        <v>121561977</v>
       </c>
       <c r="B2" t="n">
-        <v>91124</v>
+        <v>57726</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4217</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586418</v>
+        <v>586491</v>
       </c>
       <c r="R2" t="n">
-        <v>6382735</v>
+        <v>6382667</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,18 +761,12 @@
           <t>2024-12-11</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Död gren på levande tall</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121561843</v>
+        <v>121561912</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>91124</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,35 +797,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586348</v>
+        <v>586418</v>
       </c>
       <c r="R3" t="n">
-        <v>6382819</v>
+        <v>6382735</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,6 +872,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Död gren på levande tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1024,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121561863</v>
+        <v>121561809</v>
       </c>
       <c r="B5" t="n">
-        <v>90748</v>
+        <v>92039</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,26 +1039,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1071,14 +1070,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>A A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586366</v>
+        <v>586380</v>
       </c>
       <c r="R5" t="n">
-        <v>6382808</v>
+        <v>6382811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,6 +1110,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mkt anfrätt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121561809</v>
+        <v>121561822</v>
       </c>
       <c r="B6" t="n">
-        <v>92039</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,49 +1154,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A A 52918, Boarum, Sm</t>
+          <t>a 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586380</v>
+        <v>586360</v>
       </c>
       <c r="R6" t="n">
-        <v>6382811</v>
+        <v>6382810</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,11 +1226,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Mkt anfrätt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121561790</v>
+        <v>121561843</v>
       </c>
       <c r="B7" t="n">
-        <v>90748</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,38 +1265,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1308,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586486</v>
+        <v>586348</v>
       </c>
       <c r="R7" t="n">
-        <v>6382734</v>
+        <v>6382819</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121561977</v>
+        <v>121561863</v>
       </c>
       <c r="B8" t="n">
-        <v>57726</v>
+        <v>90748</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,35 +1376,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1419,13 +1415,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586491</v>
+        <v>586366</v>
       </c>
       <c r="R8" t="n">
-        <v>6382667</v>
+        <v>6382808</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,6 +1459,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1481,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121561833</v>
+        <v>121561790</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>90748</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,35 +1490,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586357</v>
+        <v>586486</v>
       </c>
       <c r="R9" t="n">
-        <v>6382811</v>
+        <v>6382734</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121561822</v>
+        <v>121561833</v>
       </c>
       <c r="B11" t="n">
         <v>98113</v>
@@ -1750,14 +1750,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>a 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586360</v>
+        <v>586357</v>
       </c>
       <c r="R11" t="n">
-        <v>6382810</v>
+        <v>6382811</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 52918-2024 artfynd.xlsx
+++ b/artfynd/A 52918-2024 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121561912</v>
+        <v>121561822</v>
       </c>
       <c r="B3" t="n">
-        <v>91124</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,49 +797,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>a 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586418</v>
+        <v>586360</v>
       </c>
       <c r="R3" t="n">
-        <v>6382735</v>
+        <v>6382810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,11 +869,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Död gren på levande tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121561956</v>
+        <v>121561843</v>
       </c>
       <c r="B4" t="n">
-        <v>57363</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,39 +908,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586567</v>
+        <v>586348</v>
       </c>
       <c r="R4" t="n">
-        <v>6382636</v>
+        <v>6382819</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,17 +982,13 @@
           <t>2024-12-11</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>I murken björkstubbe. Kanske använt 2024?</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1023,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121561809</v>
+        <v>121561863</v>
       </c>
       <c r="B5" t="n">
-        <v>92039</v>
+        <v>90748</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,26 +1023,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1070,14 +1054,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A A 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586380</v>
+        <v>586366</v>
       </c>
       <c r="R5" t="n">
-        <v>6382811</v>
+        <v>6382808</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,11 +1094,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mkt anfrätt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121561822</v>
+        <v>121561956</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>57363</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,46 +1133,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>a 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586360</v>
+        <v>586567</v>
       </c>
       <c r="R6" t="n">
-        <v>6382810</v>
+        <v>6382636</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,13 +1211,17 @@
           <t>2024-12-11</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I murken björkstubbe. Kanske använt 2024?</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1253,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121561843</v>
+        <v>121561974</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,35 +1252,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1301,13 +1292,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586348</v>
+        <v>586491</v>
       </c>
       <c r="R7" t="n">
-        <v>6382819</v>
+        <v>6382667</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,7 +1336,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1364,7 +1354,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121561863</v>
+        <v>121561790</v>
       </c>
       <c r="B8" t="n">
         <v>90748</v>
@@ -1399,7 +1389,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1415,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586366</v>
+        <v>586486</v>
       </c>
       <c r="R8" t="n">
-        <v>6382808</v>
+        <v>6382734</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121561790</v>
+        <v>121561912</v>
       </c>
       <c r="B9" t="n">
-        <v>90748</v>
+        <v>91124</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,25 +1480,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>4217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1518,7 +1508,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1529,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586486</v>
+        <v>586418</v>
       </c>
       <c r="R9" t="n">
-        <v>6382734</v>
+        <v>6382735</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,6 +1555,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Död gren på levande tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121561974</v>
+        <v>121561809</v>
       </c>
       <c r="B10" t="n">
-        <v>57510</v>
+        <v>92039</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,49 +1603,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>A A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586491</v>
+        <v>586380</v>
       </c>
       <c r="R10" t="n">
-        <v>6382667</v>
+        <v>6382811</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,12 +1676,18 @@
           <t>2024-12-11</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mkt anfrätt</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52918-2024 artfynd.xlsx
+++ b/artfynd/A 52918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121561977</v>
+        <v>121561912</v>
       </c>
       <c r="B2" t="n">
-        <v>57726</v>
+        <v>91124</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586491</v>
+        <v>586418</v>
       </c>
       <c r="R2" t="n">
-        <v>6382667</v>
+        <v>6382735</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,12 +764,18 @@
           <t>2024-12-11</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Död gren på levande tall</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121561822</v>
+        <v>121561843</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -829,14 +838,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>a 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586360</v>
+        <v>586348</v>
       </c>
       <c r="R3" t="n">
-        <v>6382810</v>
+        <v>6382819</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121561843</v>
+        <v>121561974</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,35 +917,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586348</v>
+        <v>586491</v>
       </c>
       <c r="R4" t="n">
-        <v>6382819</v>
+        <v>6382667</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,7 +1001,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121561863</v>
+        <v>121561833</v>
       </c>
       <c r="B5" t="n">
-        <v>90748</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,38 +1031,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586366</v>
+        <v>586357</v>
       </c>
       <c r="R5" t="n">
-        <v>6382808</v>
+        <v>6382811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1240,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121561974</v>
+        <v>121561822</v>
       </c>
       <c r="B7" t="n">
-        <v>57510</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,53 +1261,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>a 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586491</v>
+        <v>586360</v>
       </c>
       <c r="R7" t="n">
-        <v>6382667</v>
+        <v>6382810</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,6 +1341,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1468,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121561912</v>
+        <v>121561977</v>
       </c>
       <c r="B9" t="n">
-        <v>91124</v>
+        <v>57726</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,34 +1490,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4217</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1519,13 +1522,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586418</v>
+        <v>586491</v>
       </c>
       <c r="R9" t="n">
-        <v>6382735</v>
+        <v>6382667</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,18 +1560,12 @@
           <t>2024-12-11</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Död gren på levande tall</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1706,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121561833</v>
+        <v>121561863</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
+        <v>90748</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,35 +1715,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586357</v>
+        <v>586366</v>
       </c>
       <c r="R11" t="n">
-        <v>6382811</v>
+        <v>6382808</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 52918-2024 artfynd.xlsx
+++ b/artfynd/A 52918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121561912</v>
+        <v>121561822</v>
       </c>
       <c r="B2" t="n">
-        <v>91124</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>a 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586418</v>
+        <v>586360</v>
       </c>
       <c r="R2" t="n">
-        <v>6382735</v>
+        <v>6382810</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Död gren på levande tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121561843</v>
+        <v>121561977</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>57726</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,35 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586348</v>
+        <v>586491</v>
       </c>
       <c r="R3" t="n">
-        <v>6382819</v>
+        <v>6382667</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121561974</v>
+        <v>121561863</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>90748</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,13 +934,12 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586491</v>
+        <v>586366</v>
       </c>
       <c r="R4" t="n">
-        <v>6382667</v>
+        <v>6382808</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,6 +991,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1019,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121561833</v>
+        <v>121561956</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>57363</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,35 +1022,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586357</v>
+        <v>586567</v>
       </c>
       <c r="R5" t="n">
-        <v>6382811</v>
+        <v>6382636</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,13 +1100,17 @@
           <t>2024-12-11</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I murken björkstubbe. Kanske använt 2024?</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1130,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121561956</v>
+        <v>121561843</v>
       </c>
       <c r="B6" t="n">
-        <v>57363</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,39 +1141,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586567</v>
+        <v>586348</v>
       </c>
       <c r="R6" t="n">
-        <v>6382636</v>
+        <v>6382819</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,17 +1215,13 @@
           <t>2024-12-11</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I murken björkstubbe. Kanske använt 2024?</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1249,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121561822</v>
+        <v>121561912</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>91124</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,46 +1252,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>a 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586360</v>
+        <v>586418</v>
       </c>
       <c r="R7" t="n">
-        <v>6382810</v>
+        <v>6382735</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,6 +1327,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Död gren på levande tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121561790</v>
+        <v>121561809</v>
       </c>
       <c r="B8" t="n">
-        <v>90748</v>
+        <v>92039</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,21 +1375,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1407,14 +1406,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>A A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586486</v>
+        <v>586380</v>
       </c>
       <c r="R8" t="n">
-        <v>6382734</v>
+        <v>6382811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,6 +1446,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mkt anfrätt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121561977</v>
+        <v>121561790</v>
       </c>
       <c r="B9" t="n">
-        <v>57726</v>
+        <v>90748</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,35 +1490,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1522,13 +1529,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586491</v>
+        <v>586486</v>
       </c>
       <c r="R9" t="n">
-        <v>6382667</v>
+        <v>6382734</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1566,6 +1573,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1584,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121561809</v>
+        <v>121561974</v>
       </c>
       <c r="B10" t="n">
-        <v>92039</v>
+        <v>57510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,48 +1608,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A A 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586380</v>
+        <v>586491</v>
       </c>
       <c r="R10" t="n">
-        <v>6382811</v>
+        <v>6382667</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,18 +1682,12 @@
           <t>2024-12-11</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mkt anfrätt</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1703,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121561863</v>
+        <v>121561833</v>
       </c>
       <c r="B11" t="n">
-        <v>90748</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,38 +1718,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586366</v>
+        <v>586357</v>
       </c>
       <c r="R11" t="n">
-        <v>6382808</v>
+        <v>6382811</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 52918-2024 artfynd.xlsx
+++ b/artfynd/A 52918-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121561977</v>
+        <v>121561809</v>
       </c>
       <c r="B3" t="n">
-        <v>57726</v>
+        <v>92039</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,49 +798,52 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>A A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586491</v>
+        <v>586380</v>
       </c>
       <c r="R3" t="n">
-        <v>6382667</v>
+        <v>6382811</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,12 +875,18 @@
           <t>2024-12-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mkt anfrätt</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121561863</v>
+        <v>121561843</v>
       </c>
       <c r="B4" t="n">
-        <v>90748</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,38 +917,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586366</v>
+        <v>586348</v>
       </c>
       <c r="R4" t="n">
-        <v>6382808</v>
+        <v>6382819</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121561956</v>
+        <v>121561863</v>
       </c>
       <c r="B5" t="n">
-        <v>57363</v>
+        <v>90748</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,35 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586567</v>
+        <v>586366</v>
       </c>
       <c r="R5" t="n">
-        <v>6382636</v>
+        <v>6382808</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,17 +1105,13 @@
           <t>2024-12-11</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>I murken björkstubbe. Kanske använt 2024?</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121561843</v>
+        <v>121561974</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,35 +1142,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1177,13 +1182,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586348</v>
+        <v>586491</v>
       </c>
       <c r="R6" t="n">
-        <v>6382819</v>
+        <v>6382667</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1226,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1359,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121561809</v>
+        <v>121561977</v>
       </c>
       <c r="B8" t="n">
-        <v>92039</v>
+        <v>57726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,52 +1375,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A A 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586380</v>
+        <v>586491</v>
       </c>
       <c r="R8" t="n">
-        <v>6382811</v>
+        <v>6382667</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1448,18 +1449,12 @@
           <t>2024-12-11</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Mkt anfrätt</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1478,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121561790</v>
+        <v>121561956</v>
       </c>
       <c r="B9" t="n">
-        <v>90748</v>
+        <v>57363</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,21 +1489,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100048</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1516,12 +1511,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1529,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586486</v>
+        <v>586567</v>
       </c>
       <c r="R9" t="n">
-        <v>6382734</v>
+        <v>6382636</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,13 +1563,17 @@
           <t>2024-12-11</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I murken björkstubbe. Kanske använt 2024?</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121561974</v>
+        <v>121561790</v>
       </c>
       <c r="B10" t="n">
-        <v>57510</v>
+        <v>90748</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,35 +1608,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1644,13 +1643,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586491</v>
+        <v>586486</v>
       </c>
       <c r="R10" t="n">
-        <v>6382667</v>
+        <v>6382734</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1688,6 +1687,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52918-2024 artfynd.xlsx
+++ b/artfynd/A 52918-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121561809</v>
+        <v>121561843</v>
       </c>
       <c r="B3" t="n">
-        <v>92039</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,49 +798,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A A 52918, Boarum, Sm</t>
+          <t>A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586380</v>
+        <v>586348</v>
       </c>
       <c r="R3" t="n">
-        <v>6382811</v>
+        <v>6382819</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,11 +870,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Mkt anfrätt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121561843</v>
+        <v>121561809</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>92039</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,46 +909,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 52918, Boarum, Sm</t>
+          <t>A A 52918, Boarum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586348</v>
+        <v>586380</v>
       </c>
       <c r="R4" t="n">
-        <v>6382819</v>
+        <v>6382811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,6 +984,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mkt anfrätt</t>
         </is>
       </c>
       <c r="AD4" t="b">
